--- a/nr-doc-core-allergy-intolerance/ig/ValueSet-fr-core-vs-location-position-lit.xlsx
+++ b/nr-doc-core-allergy-intolerance/ig/ValueSet-fr-core-vs-location-position-lit.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-29T09:28:38+00:00</t>
+    <t>2026-07-20T14:26:09+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nr-doc-core-allergy-intolerance/ig/ValueSet-fr-core-vs-location-position-lit.xlsx
+++ b/nr-doc-core-allergy-intolerance/ig/ValueSet-fr-core-vs-location-position-lit.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-20T14:26:09+00:00</t>
+    <t>2026-07-20T15:52:32+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nr-doc-core-allergy-intolerance/ig/ValueSet-fr-core-vs-location-position-lit.xlsx
+++ b/nr-doc-core-allergy-intolerance/ig/ValueSet-fr-core-vs-location-position-lit.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-20T15:52:32+00:00</t>
+    <t>2026-07-31T13:08:50+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nr-doc-core-allergy-intolerance/ig/ValueSet-fr-core-vs-location-position-lit.xlsx
+++ b/nr-doc-core-allergy-intolerance/ig/ValueSet-fr-core-vs-location-position-lit.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-31T13:08:50+00:00</t>
+    <t>2026-07-31T13:11:22+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nr-doc-core-allergy-intolerance/ig/ValueSet-fr-core-vs-location-position-lit.xlsx
+++ b/nr-doc-core-allergy-intolerance/ig/ValueSet-fr-core-vs-location-position-lit.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-31T13:11:22+00:00</t>
+    <t>2026-07-31T13:13:23+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nr-doc-core-allergy-intolerance/ig/ValueSet-fr-core-vs-location-position-lit.xlsx
+++ b/nr-doc-core-allergy-intolerance/ig/ValueSet-fr-core-vs-location-position-lit.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-31T13:13:23+00:00</t>
+    <t>2026-07-31T13:21:46+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nr-doc-core-allergy-intolerance/ig/ValueSet-fr-core-vs-location-position-lit.xlsx
+++ b/nr-doc-core-allergy-intolerance/ig/ValueSet-fr-core-vs-location-position-lit.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-31T13:21:46+00:00</t>
+    <t>2026-07-31T13:27:57+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nr-doc-core-allergy-intolerance/ig/ValueSet-fr-core-vs-location-position-lit.xlsx
+++ b/nr-doc-core-allergy-intolerance/ig/ValueSet-fr-core-vs-location-position-lit.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-31T13:27:57+00:00</t>
+    <t>2026-08-03T09:32:19+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
